--- a/Result/profitability/4510.xlsx
+++ b/Result/profitability/4510.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0525</v>
+        <v>0.0475</v>
       </c>
       <c r="N2" t="n">
-        <v>18.2325</v>
+        <v>16.795</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1075</v>
+        <v>0.01750000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>17.69375</v>
+        <v>16.52625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09749999999999999</v>
+        <v>0.03750000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>17.15</v>
+        <v>15.8475</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.14125</v>
+        <v>0.0775</v>
       </c>
       <c r="N5" t="n">
-        <v>16.40875</v>
+        <v>16.0175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07500000000000001</v>
+        <v>0.0825</v>
       </c>
       <c r="N6" t="n">
-        <v>15.215</v>
+        <v>15.22625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.19</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07375000000000001</v>
+        <v>0.07375000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>15.59</v>
+        <v>15.20375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05750000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="N8" t="n">
-        <v>15.1375</v>
+        <v>14.32875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.3</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.001250000000000008</v>
+        <v>-0.001250000000000022</v>
       </c>
       <c r="N11" t="n">
         <v>13.4425</v>
@@ -1899,7 +1899,7 @@
         <v>0.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02874999999999999</v>
+        <v>0.02874999999999998</v>
       </c>
       <c r="N12" t="n">
         <v>14.06625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>461</v>
+      </c>
+      <c r="D75" t="n">
+        <v>406</v>
+      </c>
+      <c r="E75" t="n">
+        <v>54</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-53</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-11.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>259</v>
+      </c>
+      <c r="J75" t="n">
+        <v>206</v>
+      </c>
+      <c r="K75" t="n">
+        <v>116</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.06875000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.2625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.470000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3545205479452055</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.536231884057971</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.130000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2099262240107311</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
